--- a/data/gravel/Ibis Hakka MX 2025.xlsx
+++ b/data/gravel/Ibis Hakka MX 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5FE31E-50AF-F44B-AB94-28C08A8500BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAA60B7-4B00-A940-A82A-77608BDD0E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36280" yWindow="-24380" windowWidth="24960" windowHeight="14200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California, USA</t>
   </si>
 </sst>
 </file>
@@ -1473,6 +1476,9 @@
       <c r="A77" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="B77" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
